--- a/budget-nioudem.xlsx
+++ b/budget-nioudem.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="115">
   <si>
     <t xml:space="preserve">NiouDem, tableau de budget</t>
   </si>
@@ -293,19 +293,25 @@
     <t xml:space="preserve">Depenses variables notees</t>
   </si>
   <si>
-    <t xml:space="preserve">Total du journal, toutes semaines confondues.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ce qu il te reste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenus, moins les charges, moins l epargne, moins ce que tu as note.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taux d epargne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part de tes revenus qui part automatiquement de cote.</t>
+    <t xml:space="preserve">Total du journal. Tant que le mois n est pas fini, ce total est partiel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pas encore depense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenus moins charges moins epargne moins depenses notees. En cours de mois, ce chiffre est encore partiel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taux d epargne programmee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part de tes revenus qui part automatiquement de cote, avant meme de depenser.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taux d epargne reel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epargne programmee plus ce qui n a pas ete depense. Ne le lis qu une fois le mois termine.</t>
   </si>
   <si>
     <t xml:space="preserve">OU PART L ARGENT</t>
@@ -4604,7 +4610,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:E27"/>
+  <dimension ref="B2:E28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -4719,48 +4725,43 @@
         <v>93</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C13" s="29" t="n">
+        <f aca="false">IFERROR(('Revenus et charges'!C31+C11)/'Revenus et charges'!C10,0)</f>
+        <v>0.393</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="10" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <f aca="false">SUMIF(Depenses!$D$6:$D$305,B16,Depenses!$E$6:$E$305)</f>
-        <v>62</v>
-      </c>
-      <c r="D16" s="26" t="n">
-        <f aca="false">IFERROR(C16/SUM($C$16:$C$26),0)</f>
-        <v>0.626262626262626</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <f aca="false">COUNTIF(Depenses!$D$6:$D$305,B16)</f>
-        <v>1</v>
+      <c r="E16" s="9" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">SUMIF(Depenses!$D$6:$D$305,B17,Depenses!$E$6:$E$305)</f>
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="D17" s="26" t="n">
-        <f aca="false">IFERROR(C17/SUM($C$16:$C$26),0)</f>
-        <v>0.141414141414141</v>
+        <f aca="false">IFERROR(C17/SUM($C$17:$C$27),0)</f>
+        <v>0.626262626262626</v>
       </c>
       <c r="E17" s="30" t="n">
         <f aca="false">COUNTIF(Depenses!$D$6:$D$305,B17)</f>
@@ -4769,65 +4770,65 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C18" s="12" t="n">
         <f aca="false">SUMIF(Depenses!$D$6:$D$305,B18,Depenses!$E$6:$E$305)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D18" s="26" t="n">
-        <f aca="false">IFERROR(C18/SUM($C$16:$C$26),0)</f>
-        <v>0</v>
+        <f aca="false">IFERROR(C18/SUM($C$17:$C$27),0)</f>
+        <v>0.141414141414141</v>
       </c>
       <c r="E18" s="30" t="n">
         <f aca="false">COUNTIF(Depenses!$D$6:$D$305,B18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="C19" s="12" t="n">
         <f aca="false">SUMIF(Depenses!$D$6:$D$305,B19,Depenses!$E$6:$E$305)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D19" s="26" t="n">
-        <f aca="false">IFERROR(C19/SUM($C$16:$C$26),0)</f>
-        <v>0.232323232323232</v>
+        <f aca="false">IFERROR(C19/SUM($C$17:$C$27),0)</f>
+        <v>0</v>
       </c>
       <c r="E19" s="30" t="n">
         <f aca="false">COUNTIF(Depenses!$D$6:$D$305,B19)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C20" s="12" t="n">
         <f aca="false">SUMIF(Depenses!$D$6:$D$305,B20,Depenses!$E$6:$E$305)</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D20" s="26" t="n">
-        <f aca="false">IFERROR(C20/SUM($C$16:$C$26),0)</f>
-        <v>0</v>
+        <f aca="false">IFERROR(C20/SUM($C$17:$C$27),0)</f>
+        <v>0.232323232323232</v>
       </c>
       <c r="E20" s="30" t="n">
         <f aca="false">COUNTIF(Depenses!$D$6:$D$305,B20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C21" s="12" t="n">
         <f aca="false">SUMIF(Depenses!$D$6:$D$305,B21,Depenses!$E$6:$E$305)</f>
         <v>0</v>
       </c>
       <c r="D21" s="26" t="n">
-        <f aca="false">IFERROR(C21/SUM($C$16:$C$26),0)</f>
+        <f aca="false">IFERROR(C21/SUM($C$17:$C$27),0)</f>
         <v>0</v>
       </c>
       <c r="E21" s="30" t="n">
@@ -4837,14 +4838,14 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C22" s="12" t="n">
         <f aca="false">SUMIF(Depenses!$D$6:$D$305,B22,Depenses!$E$6:$E$305)</f>
         <v>0</v>
       </c>
       <c r="D22" s="26" t="n">
-        <f aca="false">IFERROR(C22/SUM($C$16:$C$26),0)</f>
+        <f aca="false">IFERROR(C22/SUM($C$17:$C$27),0)</f>
         <v>0</v>
       </c>
       <c r="E22" s="30" t="n">
@@ -4854,14 +4855,14 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C23" s="12" t="n">
         <f aca="false">SUMIF(Depenses!$D$6:$D$305,B23,Depenses!$E$6:$E$305)</f>
         <v>0</v>
       </c>
       <c r="D23" s="26" t="n">
-        <f aca="false">IFERROR(C23/SUM($C$16:$C$26),0)</f>
+        <f aca="false">IFERROR(C23/SUM($C$17:$C$27),0)</f>
         <v>0</v>
       </c>
       <c r="E23" s="30" t="n">
@@ -4871,14 +4872,14 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C24" s="12" t="n">
         <f aca="false">SUMIF(Depenses!$D$6:$D$305,B24,Depenses!$E$6:$E$305)</f>
         <v>0</v>
       </c>
       <c r="D24" s="26" t="n">
-        <f aca="false">IFERROR(C24/SUM($C$16:$C$26),0)</f>
+        <f aca="false">IFERROR(C24/SUM($C$17:$C$27),0)</f>
         <v>0</v>
       </c>
       <c r="E24" s="30" t="n">
@@ -4888,14 +4889,14 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C25" s="12" t="n">
         <f aca="false">SUMIF(Depenses!$D$6:$D$305,B25,Depenses!$E$6:$E$305)</f>
         <v>0</v>
       </c>
       <c r="D25" s="26" t="n">
-        <f aca="false">IFERROR(C25/SUM($C$16:$C$26),0)</f>
+        <f aca="false">IFERROR(C25/SUM($C$17:$C$27),0)</f>
         <v>0</v>
       </c>
       <c r="E25" s="30" t="n">
@@ -4905,14 +4906,14 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
       <c r="C26" s="12" t="n">
         <f aca="false">SUMIF(Depenses!$D$6:$D$305,B26,Depenses!$E$6:$E$305)</f>
         <v>0</v>
       </c>
       <c r="D26" s="26" t="n">
-        <f aca="false">IFERROR(C26/SUM($C$16:$C$26),0)</f>
+        <f aca="false">IFERROR(C26/SUM($C$17:$C$27),0)</f>
         <v>0</v>
       </c>
       <c r="E26" s="30" t="n">
@@ -4921,11 +4922,28 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" s="31" t="n">
-        <f aca="false">SUM(C16:C26)</f>
+      <c r="B27" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="12" t="n">
+        <f aca="false">SUMIF(Depenses!$D$6:$D$305,B27,Depenses!$E$6:$E$305)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <f aca="false">IFERROR(C27/SUM($C$17:$C$27),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="30" t="n">
+        <f aca="false">COUNTIF(Depenses!$D$6:$D$305,B27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="31" t="n">
+        <f aca="false">SUM(C17:C27)</f>
         <v>99</v>
       </c>
     </row>
@@ -4955,12 +4973,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4968,16 +4986,16 @@
         <v>68</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5528,7 +5546,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="14" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C32" s="31" t="n">
         <f aca="false">SUM(C6:C31)</f>
@@ -5545,22 +5563,22 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
